--- a/outputs/daily/predictions_2026-07-19.xlsx
+++ b/outputs/daily/predictions_2026-07-19.xlsx
@@ -924,31 +924,31 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.373524721399035</v>
+        <v>1.36524730383314</v>
       </c>
       <c r="N2" t="n">
-        <v>1.123248484254753</v>
+        <v>1.115025901820648</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.41825049294198</v>
+        <v>0.418417632755136</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3154636674178828</v>
+        <v>0.316751467606988</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2662858396401373</v>
+        <v>0.264830899637876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4207222293442246</v>
+        <v>0.4121076375087248</v>
       </c>
       <c r="T2" t="n">
-        <v>1.350271296839501</v>
+        <v>1.335221446719693</v>
       </c>
       <c r="U2" t="n">
-        <v>1.009728703160498</v>
+        <v>0.9947785532803076</v>
       </c>
       <c r="V2" t="n">
         <v>0.4460510541402212</v>
@@ -966,25 +966,25 @@
         <v>0.5586126471086718</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.4129764990032049</v>
+        <v>0.4125766708728391</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2930777818552009</v>
+        <v>0.2941924388911981</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2939457191415944</v>
+        <v>0.2932308902359629</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4553587488005468</v>
+        <v>0.4511166256419614</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5446412511994532</v>
+        <v>0.5488833743580386</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5166208564834373</v>
+        <v>0.5132406274032164</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4833791435165627</v>
+        <v>0.4867593725967836</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -992,22 +992,22 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>1.37308</v>
+        <v>1.365065</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.125925</v>
+        <v>1.115815</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.499005</v>
+        <v>2.48088</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4266621908766707</v>
+        <v>0.4266290897693416</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.261805712937817</v>
+        <v>0.2625994972724584</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.3115320961855125</v>
+        <v>0.3107714129582001</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.4266621908766707</v>
+        <v>0.4266290897693416</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.523</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.4743</v>
+        <v>0.477</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.523</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.5678</v>
+        <v>0.5682</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.4322</v>
+        <v>0.4318</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.5678</v>
+        <v>0.5682</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.539</v>
+        <v>0.5393</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>3.755363039023837</v>
+        <v>3.775994422733065</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.3115320961855125</v>
+        <v>0.3107714129582001</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.04524625654537517</v>
+        <v>0.04594051332032406</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.1699161194846923</v>
+        <v>0.1734711220750378</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1090,16 +1090,16 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>3.755363039023837</v>
+        <v>3.775994422733065</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.3115320961855125</v>
+        <v>0.3107714129582001</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.04524625654537517</v>
+        <v>0.04594051332032406</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.1699161194846923</v>
+        <v>0.1734711220750378</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>0.1397559469033217</v>
+        <v>0.1401909927302155</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>0.1004051140224423</v>
+        <v>0.1015543745887364</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>0.09505540591426083</v>
+        <v>0.096465006342243</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>0.08725374910647421</v>
+        <v>0.08699789765755364</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>0.07979478584722596</v>
+        <v>0.08060574607031619</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>0.07767982804300412</v>
+        <v>0.07802320781562194</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>0.0713548434203381</v>
+        <v>0.07105299458915473</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="CH2" t="n">
-        <v>0.05195017046919839</v>
+        <v>0.05204404681090569</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>0.04900382071469583</v>
+        <v>0.04850245464605708</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="CL2" t="n">
-        <v>0.03994839381083043</v>
+        <v>0.03959121507204219</v>
       </c>
     </row>
   </sheetData>
